--- a/xls/square_20_tri3_12.xlsx
+++ b/xls/square_20_tri3_12.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10">
+        <v>169</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10">
+        <v>441</v>
+      </c>
+      <c r="E10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10">
+        <v>121</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10">
+        <v>600</v>
+      </c>
+      <c r="I10">
+        <v>7.5314215674901135</v>
+      </c>
+      <c r="J10">
+        <v>2.5536697476237147</v>
+      </c>
+      <c r="K10">
+        <v>3.0599659368978807</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>169</v>
+      </c>
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11">
+        <v>441</v>
+      </c>
+      <c r="E11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11">
+        <v>144</v>
+      </c>
+      <c r="G11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11">
+        <v>726</v>
+      </c>
+      <c r="I11">
+        <v>4.527821967805437</v>
+      </c>
+      <c r="J11">
+        <v>0.7289767753084235</v>
+      </c>
+      <c r="K11">
+        <v>1.5549540715276635</v>
+      </c>
+    </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
         <v>11</v>
